--- a/public/files/Data_By_Towns_Index/Camden/Runnemede Borough.xlsx
+++ b/public/files/Data_By_Towns_Index/Camden/Runnemede Borough.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,385 +425,391 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>Owner Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Owner Name</t>
+          <t>Property Location</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Property Location</t>
+          <t>Municipality</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Municipality</t>
+          <t>County</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>State</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Longitude</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PATEL, ANJALI D</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PATEL, ANJALI D</t>
+          <t>601 SHERRINGTON LANE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>601 SHERRINGTON LANE</t>
+          <t>Runnemede Borough</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>-75.06020819999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.8525556</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ChIJA36sidjNxokRJZxntuWYI8Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PATEL, MAFATBHAI D &amp; VASUMATIBEN M</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>597 SHERRINGTON LANE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Runnemede Borough</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>39.8525556</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-75.06020819999999</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PATEL, BHARAT M &amp; BHAVNA B</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>29 HAVERFORD AVE</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>-75.0600463</v>
+      </c>
+      <c r="G3" t="n">
+        <v>39.8521618</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ChIJn6V6jtjNxokR-zYlkJnsVKA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PATEL, MANISH &amp; NAYANA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6 CALLIE CT.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Runnemede Borough</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>39.84686749999999</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-75.07081079999999</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PATEL, JAGDISHCHANDRA &amp; RENUKA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>28 E 10TH AVE</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>-75.05888689999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39.8538305</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ChIJAw3uN9jNxokRUyc-Zzw6Ae0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PATEL, KRUSHALI A &amp; ZINAL A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>10 CALLIE CT.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Runnemede Borough</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>39.857646</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-75.07454749999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PATEL, KRUSHALI A &amp; ZINAL A</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>10 CALLIE CT</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>-75.0590385</v>
+      </c>
+      <c r="G5" t="n">
+        <v>39.8542078</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ChIJm3JqOtjNxokRGut4jRGInkQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PATEL, YOGENDRA &amp; SUREKHA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>701 STRATFORD AVE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Runnemede Borough</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>39.8542078</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-75.0590385</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PATEL, MAFATBHAI D &amp; VASUMATIBEN M</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>597 SHERRINGTON LANE</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>-75.06268990000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>39.8544646</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ChIJayrhlHfOxokR4c9m_0ZvbNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PATEL, SHRUTIBEN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>19 E 9TH AVE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Runnemede Borough</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>39.8521618</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-75.0600463</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PATEL, MANISH &amp; NAYANA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>6 CALLIE CT</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>-75.07473469999999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>39.8571713</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ChIJowMNYmXOxokRonNmMctcV6w</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PATEL, SANGITABEN &amp; MAHENDRAK &amp;MITU</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>500 HIRSCH AVE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Runnemede Borough</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>39.8538305</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-75.05888689999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>-75.08211279999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>39.8502553</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ChIJwaiE-WrOxokRAquoPcwI1Ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SHAH, SUVARNA D</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>640 ANDREA RD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Runnemede Borough</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>-75.0879518</v>
+      </c>
+      <c r="G9" t="n">
+        <v>39.8497312</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ChIJ360qjEDOxokRhHTe6Rbw8rk</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>PATEL, MINESH &amp; BHAVANA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>58 ARDMORE AVE</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>58 ARDMORE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Runnemede Borough</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>-75.06911219999999</v>
+      </c>
+      <c r="G10" t="n">
         <v>39.8457751</v>
       </c>
-      <c r="G8" t="n">
-        <v>-75.06911219999999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PATEL, SANGITABEN &amp; MAHENDRAK &amp;MITU</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>500 HIRSCH AVE</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Runnemede Borough</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>39.8502553</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-75.08211279999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PATEL, SHRUTIBEN</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>19 E 9TH AVE</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Runnemede Borough</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>39.8571713</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-75.07473469999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PATEL, YOGENDRA &amp; SUREKHA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>701 STRATFORD AVE</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Runnemede Borough</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>39.8544646</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-75.06268990000001</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SHAH, SUVARNA D</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>640 ANDREA RD</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Runnemede Borough</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Shah</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>39.8497312</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-75.0879518</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ChIJ62DczwzOxokRKVYpx0NaAVA</t>
+        </is>
       </c>
     </row>
   </sheetData>
